--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>##</t>
   </si>
@@ -82,6 +82,9 @@
     <t>y</t>
   </si>
   <si>
+    <t>prefab</t>
+  </si>
+  <si>
     <t>equipment</t>
   </si>
   <si>
@@ -119,6 +122,9 @@
   </si>
   <si>
     <t xml:space="preserve">装备占格y </t>
+  </si>
+  <si>
+    <t>预制体地址</t>
   </si>
   <si>
     <t>换装</t>
@@ -1237,7 +1243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1249,12 +1255,12 @@
     <col min="8" max="8" width="11.6333333333333" customWidth="1"/>
     <col min="9" max="9" width="9.45" customWidth="1"/>
     <col min="10" max="10" width="13.6916666666667" customWidth="1"/>
-    <col min="11" max="13" width="11.9583333333333" customWidth="1"/>
-    <col min="14" max="14" width="20.2083333333333" customWidth="1"/>
-    <col min="15" max="15" width="72.6416666666667" customWidth="1"/>
+    <col min="11" max="14" width="11.9583333333333" customWidth="1"/>
+    <col min="15" max="15" width="20.2083333333333" customWidth="1"/>
+    <col min="16" max="16" width="72.6416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1300,71 +1306,77 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="87" spans="1:15">
+    <row r="2" ht="87" spans="1:16">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:15">
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1372,16 +1384,17 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="N3" s="7"/>
       <c r="O3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="1:15">
+    <row r="6" ht="28.5" spans="1:16">
       <c r="A6" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="9">
         <v>530001</v>
@@ -1390,13 +1403,13 @@
         <v>530001</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" s="9">
         <v>530001</v>
@@ -1417,14 +1430,15 @@
         <v>2</v>
       </c>
       <c r="M6" s="10"/>
-      <c r="N6" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="N6" s="10"/>
       <c r="O6" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1438,12 +1452,13 @@
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
-      <c r="N7" s="11"/>
+      <c r="N7" s="10"/>
       <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
-    <row r="8" ht="28.5" spans="1:15">
+    <row r="8" ht="28.5" spans="1:16">
       <c r="A8" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="9">
         <v>540001</v>
@@ -1452,13 +1467,13 @@
         <v>540001</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" s="9">
         <v>540001</v>
@@ -1479,16 +1494,17 @@
         <v>3</v>
       </c>
       <c r="M8" s="10"/>
-      <c r="N8" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="N8" s="10"/>
       <c r="O8" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9" ht="28.5" spans="1:15">
+    <row r="9" ht="28.5" spans="1:16">
       <c r="A9" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9">
         <v>540002</v>
@@ -1497,13 +1513,13 @@
         <v>540002</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" s="9">
         <v>540002</v>
@@ -1524,16 +1540,17 @@
         <v>3</v>
       </c>
       <c r="M9" s="10"/>
-      <c r="N9" s="11" t="s">
-        <v>47</v>
-      </c>
+      <c r="N9" s="10"/>
       <c r="O9" s="11" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="10" ht="28.5" spans="1:15">
+    <row r="10" ht="28.5" spans="1:16">
       <c r="A10" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="9">
         <v>560001</v>
@@ -1542,13 +1559,13 @@
         <v>540003</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" s="9">
         <v>540003</v>
@@ -1569,16 +1586,17 @@
         <v>2</v>
       </c>
       <c r="M10" s="10"/>
-      <c r="N10" s="11" t="s">
-        <v>50</v>
-      </c>
+      <c r="N10" s="10"/>
       <c r="O10" s="11" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 E6:E9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E10">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>##</t>
   </si>
@@ -76,24 +76,12 @@
     <t>tradeValue</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>prefab</t>
   </si>
   <si>
-    <t>equipment</t>
-  </si>
-  <si>
     <t>icon</t>
   </si>
   <si>
-    <t>attrModifier</t>
-  </si>
-  <si>
     <t>道具编号</t>
   </si>
   <si>
@@ -118,22 +106,10 @@
     <t>交易价值</t>
   </si>
   <si>
-    <t xml:space="preserve">装备占格x </t>
-  </si>
-  <si>
-    <t xml:space="preserve">装备占格y </t>
-  </si>
-  <si>
     <t>预制体地址</t>
   </si>
   <si>
-    <t>换装</t>
-  </si>
-  <si>
     <t>道具图标</t>
-  </si>
-  <si>
-    <t>属性修改器</t>
   </si>
   <si>
     <r>
@@ -165,24 +141,20 @@
   </si>
   <si>
     <t>5x0xxx
-"0：主手"
-"1：副手"
-"2：双手"
-"3：头盔"
-"4：护甲"
-"5：护手"
-"6：鞋子"</t>
+"0：武器"
+"1：头盔"
+"2：面具"
+"3：护甲"
+"4：鞋子"</t>
   </si>
   <si>
     <t>参见道具类别备注</t>
   </si>
   <si>
-    <t xml:space="preserve">主手
-副手
-双手
+    <t xml:space="preserve">武器
 头盔
+面具
 护甲
-护手
 鞋子
 </t>
   </si>
@@ -193,25 +165,37 @@
     <t>资源路径位于？？？</t>
   </si>
   <si>
-    <t>(list#sep=|),(Defination.AttributeModifier#sep=,)</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
-    <t>测试头盔</t>
+    <t>普通短剑</t>
   </si>
   <si>
     <t>装备</t>
   </si>
   <si>
-    <t>头盔</t>
-  </si>
-  <si>
-    <t>Equip/Helmet/T_Helmet_001</t>
-  </si>
-  <si>
-    <t>ATK,TAdd,1|MHP,TAdd,20</t>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>Weapon/Wep_Sword_01</t>
+  </si>
+  <si>
+    <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
+  </si>
+  <si>
+    <t>普通弩箭</t>
+  </si>
+  <si>
+    <t>Weapon/Wep_CrossBow_01</t>
+  </si>
+  <si>
+    <t>Icons/Weapon/Sp_Icon_Weapon_CrossBow_01</t>
+  </si>
+  <si>
+    <t>普通重锤</t>
+  </si>
+  <si>
+    <t>Icons/Weapon/Sp_Icon_Weapon_Hammer_01</t>
   </si>
   <si>
     <t>测试护甲</t>
@@ -226,7 +210,7 @@
     <t>测试护甲2</t>
   </si>
   <si>
-    <t>护腿</t>
+    <t>面具</t>
   </si>
   <si>
     <t>Equip/Armor/T_Armor_002</t>
@@ -251,8 +235,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -750,133 +742,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -884,19 +876,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,360 +1236,363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12.9333333333333" customWidth="1"/>
-    <col min="3" max="3" width="9.44166666666667" customWidth="1"/>
-    <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="5" width="7.175" customWidth="1"/>
+    <col min="3" max="3" width="16.7583333333333" customWidth="1"/>
+    <col min="4" max="4" width="30.2833333333333" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
     <col min="6" max="7" width="8.9" customWidth="1"/>
     <col min="8" max="8" width="11.6333333333333" customWidth="1"/>
     <col min="9" max="9" width="9.45" customWidth="1"/>
     <col min="10" max="10" width="13.6916666666667" customWidth="1"/>
-    <col min="11" max="14" width="11.9583333333333" customWidth="1"/>
-    <col min="15" max="15" width="20.2083333333333" customWidth="1"/>
-    <col min="16" max="16" width="72.6416666666667" customWidth="1"/>
+    <col min="11" max="11" width="22.7916666666667" customWidth="1"/>
+    <col min="12" max="12" width="20.2083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+    </row>
+    <row r="2" ht="72.75" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="G2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" ht="87" spans="1:16">
-      <c r="A2" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:12">
+      <c r="A3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:12">
+      <c r="A5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10">
+        <v>500001</v>
+      </c>
+      <c r="C5" s="10">
+        <v>500001</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="10">
+        <v>530001</v>
+      </c>
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="4" t="s">
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:12">
+      <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
+      <c r="B6" s="10">
+        <v>500002</v>
+      </c>
+      <c r="C6" s="10">
+        <v>500002</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="10">
+        <v>530003</v>
+      </c>
+      <c r="H6" s="11">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:16">
-      <c r="A3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="7" ht="28.5" spans="1:12">
+      <c r="A7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="10">
+        <v>500003</v>
+      </c>
+      <c r="C7" s="10">
+        <v>500003</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7" t="s">
+      <c r="G7" s="10">
+        <v>530003</v>
+      </c>
+      <c r="H7" s="11">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>37</v>
+      <c r="L7" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="1:16">
-      <c r="A6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="9">
-        <v>530001</v>
-      </c>
-      <c r="C6" s="9">
-        <v>530001</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="9" t="s">
+    <row r="8" spans="1:12">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:12">
+      <c r="A9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10">
+        <v>540001</v>
+      </c>
+      <c r="C9" s="10">
+        <v>540001</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="E9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="9">
-        <v>530001</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="G9" s="10">
+        <v>540001</v>
+      </c>
+      <c r="H9" s="11">
         <v>1</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I9" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J9" s="11">
         <v>1</v>
       </c>
-      <c r="K6" s="10">
-        <v>2</v>
-      </c>
-      <c r="L6" s="10">
-        <v>2</v>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11" t="s">
+      <c r="K9" s="11"/>
+      <c r="L9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="P6" s="11" t="s">
+    </row>
+    <row r="10" ht="28.5" spans="1:12">
+      <c r="A10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="10">
+        <v>540002</v>
+      </c>
+      <c r="C10" s="10">
+        <v>540002</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>43</v>
       </c>
+      <c r="E10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10">
+        <v>540002</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:16">
-      <c r="A8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="9">
-        <v>540001</v>
-      </c>
-      <c r="C8" s="9">
-        <v>540001</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="9">
-        <v>540001</v>
-      </c>
-      <c r="H8" s="10">
+    <row r="11" ht="28.5" spans="1:12">
+      <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="10">
+        <v>560001</v>
+      </c>
+      <c r="C11" s="10">
+        <v>540003</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="10">
+        <v>540003</v>
+      </c>
+      <c r="H11" s="11">
         <v>1</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I11" s="11">
         <v>0</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J11" s="11">
         <v>1</v>
       </c>
-      <c r="K8" s="10">
-        <v>2</v>
-      </c>
-      <c r="L8" s="10">
-        <v>3</v>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:16">
-      <c r="A9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="9">
-        <v>540002</v>
-      </c>
-      <c r="C9" s="9">
-        <v>540002</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="K11" s="11"/>
+      <c r="L11" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="G9" s="9">
-        <v>540002</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <v>1</v>
-      </c>
-      <c r="K9" s="10">
-        <v>2</v>
-      </c>
-      <c r="L9" s="10">
-        <v>3</v>
-      </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" ht="28.5" spans="1:16">
-      <c r="A10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="9">
-        <v>560001</v>
-      </c>
-      <c r="C10" s="9">
-        <v>540003</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="9">
-        <v>540003</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="10">
-        <v>0</v>
-      </c>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10">
-        <v>2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>2</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E6 E7 E8:E11">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>##</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
   <si>
     <t>name_cn</t>
@@ -168,6 +171,12 @@
     <t>是</t>
   </si>
   <si>
+    <t>name_500001</t>
+  </si>
+  <si>
+    <t>Category.OneHand</t>
+  </si>
+  <si>
     <t>普通短剑</t>
   </si>
   <si>
@@ -177,22 +186,43 @@
     <t>武器</t>
   </si>
   <si>
+    <t>desc_500001</t>
+  </si>
+  <si>
     <t>Weapon/Wep_Sword_01</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
   </si>
   <si>
+    <t>name_500002</t>
+  </si>
+  <si>
+    <t>Category.Ranged</t>
+  </si>
+  <si>
     <t>普通弩箭</t>
   </si>
   <si>
+    <t>desc_500002</t>
+  </si>
+  <si>
     <t>Weapon/Wep_CrossBow_01</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_CrossBow_01</t>
   </si>
   <si>
+    <t>name_500003</t>
+  </si>
+  <si>
+    <t>Category.HeavyBlunt</t>
+  </si>
+  <si>
     <t>普通重锤</t>
+  </si>
+  <si>
+    <t>desc_500003</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Hammer_01</t>
@@ -1236,23 +1266,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12.9333333333333" customWidth="1"/>
     <col min="3" max="3" width="16.7583333333333" customWidth="1"/>
-    <col min="4" max="4" width="30.2833333333333" customWidth="1"/>
-    <col min="5" max="5" width="32.5" customWidth="1"/>
-    <col min="6" max="7" width="8.9" customWidth="1"/>
-    <col min="8" max="8" width="11.6333333333333" customWidth="1"/>
-    <col min="9" max="9" width="9.45" customWidth="1"/>
-    <col min="10" max="10" width="13.6916666666667" customWidth="1"/>
-    <col min="11" max="11" width="22.7916666666667" customWidth="1"/>
-    <col min="12" max="12" width="20.2083333333333" customWidth="1"/>
+    <col min="4" max="5" width="25.875" customWidth="1"/>
+    <col min="6" max="6" width="9.55833333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.725" customWidth="1"/>
+    <col min="8" max="8" width="8.9" customWidth="1"/>
+    <col min="9" max="9" width="11.6333333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.45" customWidth="1"/>
+    <col min="11" max="11" width="13.6916666666667" customWidth="1"/>
+    <col min="12" max="12" width="22.7916666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.2083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1289,28 +1320,29 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="72.75" spans="1:12">
+    <row r="2" ht="72.75" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -1325,150 +1357,163 @@
       <c r="L2" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="M2" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:12">
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:13">
       <c r="A3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
-      <c r="L3" s="8" t="s">
-        <v>28</v>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:12">
+    <row r="5" ht="28.5" spans="1:13">
       <c r="A5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="10">
         <v>500001</v>
       </c>
-      <c r="C5" s="10">
-        <v>500001</v>
+      <c r="C5" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>1</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:13">
+      <c r="A6" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="10">
-        <v>530001</v>
-      </c>
-      <c r="H5" s="11">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11">
-        <v>1</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:12">
-      <c r="A6" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="B6" s="10">
         <v>500002</v>
       </c>
-      <c r="C6" s="10">
-        <v>500002</v>
+      <c r="C6" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="10">
-        <v>530003</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="11">
         <v>1</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>1</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>37</v>
+      <c r="L6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:12">
+    <row r="7" ht="28.5" spans="1:13">
       <c r="A7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="10">
         <v>500003</v>
       </c>
-      <c r="C7" s="10">
-        <v>500003</v>
+      <c r="C7" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="10">
-        <v>530003</v>
-      </c>
-      <c r="H7" s="11">
+        <v>34</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="11">
         <v>1</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>1</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>39</v>
+      <c r="L7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1476,15 +1521,16 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="12"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="12"/>
     </row>
-    <row r="9" ht="28.5" spans="1:12">
+    <row r="9" ht="28.5" spans="1:13">
       <c r="A9" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
         <v>540001</v>
@@ -1492,35 +1538,36 @@
       <c r="C9" s="10">
         <v>540001</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="10">
+        <v>34</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="10">
         <v>540001</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="11">
         <v>1</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>1</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="12" t="s">
-        <v>42</v>
+      <c r="L9" s="11"/>
+      <c r="M9" s="12" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="10" ht="28.5" spans="1:12">
+    <row r="10" ht="28.5" spans="1:13">
       <c r="A10" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="10">
         <v>540002</v>
@@ -1528,35 +1575,36 @@
       <c r="C10" s="10">
         <v>540002</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>43</v>
-      </c>
+      <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="10">
+        <v>34</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="10">
         <v>540002</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="11">
         <v>1</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>1</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="12" t="s">
-        <v>45</v>
+      <c r="L10" s="11"/>
+      <c r="M10" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="11" ht="28.5" spans="1:12">
+    <row r="11" ht="28.5" spans="1:13">
       <c r="A11" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="10">
         <v>560001</v>
@@ -1564,35 +1612,36 @@
       <c r="C11" s="10">
         <v>540003</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="10">
+        <v>34</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="10">
         <v>540003</v>
       </c>
-      <c r="H11" s="11">
+      <c r="I11" s="11">
         <v>1</v>
       </c>
-      <c r="I11" s="11">
+      <c r="J11" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="11">
+      <c r="K11" s="11">
         <v>1</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="12" t="s">
-        <v>48</v>
+      <c r="L11" s="11"/>
+      <c r="M11" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E6 E7 E8:E11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F11">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity\ProjectTinyRpg\Luban\DataTables\Datas\Item\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
   </bookViews>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
   <si>
     <t>##</t>
   </si>
@@ -52,9 +57,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -67,9 +69,6 @@
     <t>equipType</t>
   </si>
   <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>rarity</t>
   </si>
   <si>
@@ -88,16 +87,10 @@
     <t>道具编号</t>
   </si>
   <si>
-    <t>道具名称</t>
-  </si>
-  <si>
     <t>道具类别</t>
   </si>
   <si>
     <t>装备类型</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>品质</t>
@@ -143,37 +136,23 @@
 CCCC表示编号</t>
   </si>
   <si>
-    <t>5x0xxx
-"0：武器"
-"1：头盔"
-"2：面具"
-"3：护甲"
-"4：鞋子"</t>
-  </si>
-  <si>
     <t>参见道具类别备注</t>
   </si>
   <si>
     <t xml:space="preserve">武器
 头盔
-面具
 护甲
 鞋子
+首饰
 </t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>资源路径位于？？？</t>
   </si>
   <si>
     <t>是</t>
   </si>
   <si>
-    <t>name_500001</t>
-  </si>
-  <si>
     <t>Category.OneHand</t>
   </si>
   <si>
@@ -186,73 +165,85 @@
     <t>武器</t>
   </si>
   <si>
-    <t>desc_500001</t>
-  </si>
-  <si>
     <t>Weapon/Wep_Sword_01</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
   </si>
   <si>
-    <t>name_500002</t>
-  </si>
-  <si>
     <t>Category.Ranged</t>
   </si>
   <si>
     <t>普通弩箭</t>
   </si>
   <si>
-    <t>desc_500002</t>
-  </si>
-  <si>
     <t>Weapon/Wep_CrossBow_01</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_CrossBow_01</t>
   </si>
   <si>
-    <t>name_500003</t>
-  </si>
-  <si>
     <t>Category.HeavyBlunt</t>
   </si>
   <si>
     <t>普通重锤</t>
   </si>
   <si>
-    <t>desc_500003</t>
+    <t>Weapon/Wep_Hammer_01</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Hammer_01</t>
   </si>
   <si>
-    <t>测试护甲</t>
+    <t>Category.Armor</t>
+  </si>
+  <si>
+    <t>普通头盔</t>
+  </si>
+  <si>
+    <t>头盔</t>
+  </si>
+  <si>
+    <t>Icons/Armor/Sp_Icon_Armor_Helmet_01</t>
+  </si>
+  <si>
+    <t>普通护甲</t>
   </si>
   <si>
     <t>护甲</t>
   </si>
   <si>
-    <t>Equip/Armor/T_Armor_001</t>
-  </si>
-  <si>
-    <t>测试护甲2</t>
-  </si>
-  <si>
-    <t>面具</t>
-  </si>
-  <si>
-    <t>Equip/Armor/T_Armor_002</t>
-  </si>
-  <si>
-    <t>测试鞋子</t>
+    <t>Icons/Armor/Sp_Icon_Armor_Chestplate_01</t>
+  </si>
+  <si>
+    <t>普通鞋子</t>
   </si>
   <si>
     <t>鞋子</t>
   </si>
   <si>
-    <t>Equip/Boots/T_Boots_001</t>
+    <t>Icons/Armor/Sp_Icon_Armor_Boots_01</t>
+  </si>
+  <si>
+    <t>Category.Accessory</t>
+  </si>
+  <si>
+    <t>普通项链</t>
+  </si>
+  <si>
+    <t>首饰</t>
+  </si>
+  <si>
+    <t>Icons/Accessory/Sp_Icon_Accessory_Necklace_01</t>
+  </si>
+  <si>
+    <t>Icons/Armor/Sp_Icon_Armor_Helmet_02</t>
+  </si>
+  <si>
+    <t>Icons/Armor/Sp_Icon_Armor_Chestplate_02</t>
+  </si>
+  <si>
+    <t>Icons/Armor/Sp_Icon_Armor_Boots_02</t>
   </si>
 </sst>
 </file>
@@ -433,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +440,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,7 +775,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -802,16 +799,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -820,85 +817,85 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -906,7 +903,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -929,6 +926,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1266,24 +1272,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="12.9333333333333" customWidth="1"/>
-    <col min="3" max="3" width="16.7583333333333" customWidth="1"/>
-    <col min="4" max="5" width="25.875" customWidth="1"/>
-    <col min="6" max="6" width="9.55833333333333" customWidth="1"/>
-    <col min="7" max="7" width="10.725" customWidth="1"/>
-    <col min="8" max="8" width="8.9" customWidth="1"/>
-    <col min="9" max="9" width="11.6333333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.45" customWidth="1"/>
-    <col min="11" max="11" width="13.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="22.7916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.2083333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.1166666666667" customWidth="1"/>
+    <col min="3" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="9.55833333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.725" customWidth="1"/>
+    <col min="7" max="7" width="11.6333333333333" customWidth="1"/>
+    <col min="8" max="8" width="9.45" customWidth="1"/>
+    <col min="9" max="9" width="13.6916666666667" customWidth="1"/>
+    <col min="10" max="10" width="22.7916666666667" customWidth="1"/>
+    <col min="11" max="11" width="37.35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1317,331 +1321,413 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" ht="72.75" spans="1:13">
+    <row r="2" ht="72.75" spans="1:11">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+    </row>
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:11">
+      <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:13">
-      <c r="A3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8" t="s">
-        <v>29</v>
+      <c r="K3" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:13">
+    <row r="5" ht="28.5" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B5" s="10">
         <v>500001</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>36</v>
+        <v>28</v>
+      </c>
+      <c r="G5" s="11">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="b">
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
       </c>
-      <c r="J5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11">
-        <v>1</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>38</v>
+      <c r="J5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:13">
+    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:11">
       <c r="A6" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6" s="10">
         <v>500002</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1</v>
+      </c>
+      <c r="H6" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="11">
-        <v>1</v>
-      </c>
-      <c r="J6" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="11">
-        <v>1</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>44</v>
-      </c>
     </row>
-    <row r="7" ht="28.5" spans="1:13">
+    <row r="7" ht="28.5" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B7" s="10">
         <v>500003</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="11">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="10">
+        <v>510001</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="10">
+        <v>520001</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="10" t="s">
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="10">
+        <v>530001</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G11" s="11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="11">
-        <v>1</v>
-      </c>
-      <c r="J7" s="11" t="b">
+    </row>
+    <row r="14" ht="28.5" spans="1:11">
+      <c r="A14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="10">
+        <v>540001</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="11">
-        <v>1</v>
-      </c>
-      <c r="L7" s="11" t="s">
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="10">
+        <v>510002</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="10">
+        <v>520002</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>49</v>
+      <c r="E17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="11">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="12"/>
-    </row>
-    <row r="9" ht="28.5" spans="1:13">
-      <c r="A9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="10">
-        <v>540001</v>
-      </c>
-      <c r="C9" s="10">
-        <v>540001</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="10">
-        <v>540001</v>
-      </c>
-      <c r="I9" s="11">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="b">
+    <row r="18" spans="1:11">
+      <c r="A18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="10">
+        <v>530002</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="11">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="11">
-        <v>1</v>
-      </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" ht="28.5" spans="1:13">
-      <c r="A10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10">
-        <v>540002</v>
-      </c>
-      <c r="C10" s="10">
-        <v>540002</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="10">
-        <v>540002</v>
-      </c>
-      <c r="I10" s="11">
-        <v>1</v>
-      </c>
-      <c r="J10" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11">
-        <v>1</v>
-      </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="12" t="s">
+      <c r="I18" s="11">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="28.5" spans="1:13">
-      <c r="A11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="10">
-        <v>560001</v>
-      </c>
-      <c r="C11" s="10">
-        <v>540003</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="10">
-        <v>540003</v>
-      </c>
-      <c r="I11" s="11">
-        <v>1</v>
-      </c>
-      <c r="J11" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11">
-        <v>1</v>
-      </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 E11 E14 E16 E17 E18 E5:E9">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>##</t>
   </si>
@@ -84,6 +84,9 @@
     <t>icon</t>
   </si>
   <si>
+    <t>*Modifier</t>
+  </si>
+  <si>
     <t>道具编号</t>
   </si>
   <si>
@@ -106,6 +109,15 @@
   </si>
   <si>
     <t>道具图标</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
   <si>
     <r>
@@ -150,6 +162,18 @@
     <t>资源路径位于？？？</t>
   </si>
   <si>
+    <t>属性类型</t>
+  </si>
+  <si>
+    <t>加算基础值
+加算百分比
+乘算百分比
+加算最终值</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
@@ -169,6 +193,15 @@
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>加算基础值</t>
+  </si>
+  <si>
+    <t>物穿</t>
   </si>
   <si>
     <t>Category.Ranged</t>
@@ -630,7 +663,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -648,6 +681,28 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -775,7 +830,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -787,34 +842,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -903,7 +958,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -913,12 +968,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
@@ -936,6 +1003,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1272,7 +1351,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1285,9 +1364,12 @@
     <col min="9" max="9" width="13.6916666666667" customWidth="1"/>
     <col min="10" max="10" width="22.7916666666667" customWidth="1"/>
     <col min="11" max="11" width="37.35" customWidth="1"/>
+    <col min="12" max="12" width="17.6416666666667" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="14" width="21.7583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1321,413 +1403,531 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
-    <row r="2" ht="72.75" spans="1:11">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="72.75" spans="1:14">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:11">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8" t="s">
+    <row r="3" s="2" customFormat="1" ht="85" customHeight="1" spans="1:14">
+      <c r="A3" s="11" t="s">
         <v>23</v>
       </c>
+      <c r="B3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" ht="28.5" spans="1:11">
-      <c r="A5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="10">
+    <row r="5" spans="1:14">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="14">
         <v>500001</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="11">
-        <v>1</v>
-      </c>
-      <c r="H5" s="11" t="b">
+      <c r="C5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="15">
+        <v>1</v>
+      </c>
+      <c r="H5" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="11">
-        <v>1</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>30</v>
+      <c r="I5" s="15">
+        <v>1</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="18">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="10">
+    <row r="6" s="3" customFormat="1" spans="1:14">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:14">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="28.5" spans="1:14">
+      <c r="A8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="14">
         <v>500002</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:14">
+      <c r="A9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1</v>
-      </c>
-      <c r="H6" s="11" t="b">
+      <c r="B9" s="14">
+        <v>500003</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="11">
-        <v>1</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="14">
+        <v>510001</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>34</v>
       </c>
+      <c r="F11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="10">
-        <v>500003</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="11">
-        <v>1</v>
-      </c>
-      <c r="H7" s="11" t="b">
+    <row r="12" spans="1:14">
+      <c r="A12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="14">
+        <v>520001</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="11">
-        <v>1</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>38</v>
-      </c>
+      <c r="I12" s="15">
+        <v>1</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
+    <row r="13" spans="1:14">
+      <c r="A13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="14">
+        <v>530001</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="10">
-        <v>510001</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="11">
-        <v>1</v>
-      </c>
-      <c r="H9" s="11" t="b">
+    <row r="14" spans="1:14">
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+    </row>
+    <row r="16" ht="28.5" spans="1:14">
+      <c r="A16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540001</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="11">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="I16" s="15">
+        <v>1</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="10">
-        <v>520001</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="11">
-        <v>1</v>
-      </c>
-      <c r="H10" s="11" t="b">
+    <row r="17" spans="1:14">
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="14">
+        <v>510002</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="11">
-        <v>1</v>
-      </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12" t="s">
-        <v>45</v>
-      </c>
+      <c r="I18" s="15">
+        <v>1</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="10">
-        <v>530001</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="11" t="b">
+    <row r="19" spans="1:14">
+      <c r="A19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="14">
+        <v>520002</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="11">
-        <v>1</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="I19" s="15">
+        <v>1</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
     </row>
-    <row r="14" ht="28.5" spans="1:11">
-      <c r="A14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="10">
-        <v>540001</v>
-      </c>
-      <c r="C14" s="10" t="s">
+    <row r="20" spans="1:14">
+      <c r="A20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="14">
+        <v>530002</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="11">
-        <v>1</v>
-      </c>
-      <c r="H14" s="11" t="b">
+      <c r="D20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="11">
-        <v>1</v>
-      </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="10">
-        <v>510002</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="11">
-        <v>1</v>
-      </c>
-      <c r="H16" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="11">
-        <v>1</v>
-      </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="10">
-        <v>520002</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="11">
-        <v>1</v>
-      </c>
-      <c r="H17" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="11">
-        <v>1</v>
-      </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="10">
-        <v>530002</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="11">
-        <v>1</v>
-      </c>
-      <c r="H18" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="11">
-        <v>1</v>
-      </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="12" t="s">
-        <v>55</v>
-      </c>
+      <c r="I20" s="15">
+        <v>1</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L1:N1"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 E11 E14 E16 E17 E18 E5:E9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16 E5:E13 E18:E20">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="装备表" sheetId="3" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>##</t>
   </si>
@@ -177,30 +177,39 @@
     <t>是</t>
   </si>
   <si>
+    <t>Category.Unarmed</t>
+  </si>
+  <si>
+    <t>赤手空拳</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>Weapon/Wep_Sword_01.prefab</t>
+  </si>
+  <si>
+    <t>Icons/Weapon/Sp_Icon_Weapon_Unarmed</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>加算基础值</t>
+  </si>
+  <si>
     <t>Category.OneHand</t>
   </si>
   <si>
     <t>普通短剑</t>
   </si>
   <si>
-    <t>装备</t>
-  </si>
-  <si>
-    <t>武器</t>
-  </si>
-  <si>
-    <t>Weapon/Wep_Sword_01</t>
-  </si>
-  <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
   </si>
   <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>加算基础值</t>
-  </si>
-  <si>
     <t>物穿</t>
   </si>
   <si>
@@ -210,7 +219,7 @@
     <t>普通弩箭</t>
   </si>
   <si>
-    <t>Weapon/Wep_CrossBow_01</t>
+    <t>Weapon/Wep_CrossBow_01.prefab</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_CrossBow_01</t>
@@ -222,7 +231,7 @@
     <t>普通重锤</t>
   </si>
   <si>
-    <t>Weapon/Wep_Hammer_01</t>
+    <t>Weapon/Wep_Hammer_01.prefab</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Hammer_01</t>
@@ -1351,7 +1360,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1362,7 +1371,7 @@
     <col min="7" max="7" width="11.6333333333333" customWidth="1"/>
     <col min="8" max="8" width="9.45" customWidth="1"/>
     <col min="9" max="9" width="13.6916666666667" customWidth="1"/>
-    <col min="10" max="10" width="22.7916666666667" customWidth="1"/>
+    <col min="10" max="10" width="29.85" customWidth="1"/>
     <col min="11" max="11" width="37.35" customWidth="1"/>
     <col min="12" max="12" width="17.6416666666667" customWidth="1"/>
     <col min="13" max="13" width="15.875" customWidth="1"/>
@@ -1525,25 +1534,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:14">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="19" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="14">
+        <v>500001</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>40</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="15">
+        <v>1</v>
+      </c>
+      <c r="H6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="M6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="18">
         <v>1</v>
       </c>
     </row>
@@ -1559,60 +1590,44 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="16"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
+      <c r="L7" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="20">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="28.5" spans="1:14">
-      <c r="A8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="14">
-        <v>500002</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <v>1</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>44</v>
-      </c>
+    <row r="8" s="3" customFormat="1" spans="1:14">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
     </row>
-    <row r="9" ht="28.5" spans="1:14">
+    <row r="9" s="3" customFormat="1" ht="28.5" spans="1:14">
       <c r="A9" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="14">
-        <v>500003</v>
+        <v>500002</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>34</v>
@@ -1630,63 +1645,65 @@
         <v>1</v>
       </c>
       <c r="J9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" ht="28.5" spans="1:14">
+      <c r="A10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="14">
+        <v>500003</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
+      <c r="D10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="14">
-        <v>510001</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="15">
-        <v>1</v>
-      </c>
-      <c r="H11" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
-        <v>1</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16" t="s">
-        <v>52</v>
-      </c>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -1696,10 +1713,10 @@
         <v>31</v>
       </c>
       <c r="B12" s="14">
-        <v>520001</v>
+        <v>510001</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>53</v>
@@ -1732,10 +1749,10 @@
         <v>31</v>
       </c>
       <c r="B13" s="14">
-        <v>530001</v>
+        <v>520001</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>56</v>
@@ -1764,6 +1781,37 @@
       <c r="N13" s="18"/>
     </row>
     <row r="14" spans="1:14">
+      <c r="A14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="14">
+        <v>530001</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
+        <v>1</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -1773,79 +1821,48 @@
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
     </row>
-    <row r="16" ht="28.5" spans="1:14">
-      <c r="A16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="14">
-        <v>540001</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <v>1</v>
-      </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16" t="s">
-        <v>62</v>
-      </c>
+    <row r="16" spans="1:14">
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" ht="28.5" spans="1:14">
+      <c r="A17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="14">
+        <v>540001</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
+        <v>1</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="14">
-        <v>510002</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="15">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="15">
-        <v>1</v>
-      </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
@@ -1855,10 +1872,10 @@
         <v>31</v>
       </c>
       <c r="B19" s="14">
-        <v>520002</v>
+        <v>510002</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>53</v>
@@ -1880,7 +1897,7 @@
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
@@ -1891,10 +1908,10 @@
         <v>31</v>
       </c>
       <c r="B20" s="14">
-        <v>530002</v>
+        <v>520002</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>56</v>
@@ -1916,18 +1933,54 @@
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="14">
+        <v>530002</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
+        <v>1</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L1:N1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16 E5:E13 E18:E20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E17 E6:E14 E19:E21">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/装备系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/装备系统表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="装备表" sheetId="3" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>##</t>
   </si>
@@ -177,10 +177,10 @@
     <t>是</t>
   </si>
   <si>
-    <t>Category.Unarmed</t>
-  </si>
-  <si>
-    <t>赤手空拳</t>
+    <t>Category.OneHand</t>
+  </si>
+  <si>
+    <t>普通短剑</t>
   </si>
   <si>
     <t>装备</t>
@@ -189,10 +189,10 @@
     <t>武器</t>
   </si>
   <si>
-    <t>Weapon/Wep_Sword_01.prefab</t>
-  </si>
-  <si>
-    <t>Icons/Weapon/Sp_Icon_Weapon_Unarmed</t>
+    <t>Weapon/Player/Wep_Sword_01.prefab</t>
+  </si>
+  <si>
+    <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
   </si>
   <si>
     <t>攻击</t>
@@ -201,25 +201,22 @@
     <t>加算基础值</t>
   </si>
   <si>
-    <t>Category.OneHand</t>
-  </si>
-  <si>
-    <t>普通短剑</t>
-  </si>
-  <si>
-    <t>Icons/Weapon/Sp_Icon_Weapon_Sword_01</t>
-  </si>
-  <si>
     <t>物穿</t>
   </si>
   <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>加算最终值</t>
+  </si>
+  <si>
     <t>Category.Ranged</t>
   </si>
   <si>
     <t>普通弩箭</t>
   </si>
   <si>
-    <t>Weapon/Wep_CrossBow_01.prefab</t>
+    <t>Weapon/Player/Wep_CrossBow_01.prefab</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_CrossBow_01</t>
@@ -231,7 +228,7 @@
     <t>普通重锤</t>
   </si>
   <si>
-    <t>Weapon/Wep_Hammer_01.prefab</t>
+    <t>Weapon/Player/Wep_Hammer_01.prefab</t>
   </si>
   <si>
     <t>Icons/Weapon/Sp_Icon_Weapon_Hammer_01</t>
@@ -1360,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1534,47 +1531,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="14">
-        <v>500001</v>
-      </c>
-      <c r="C6" s="14" t="s">
+    <row r="6" s="3" customFormat="1" spans="1:14">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1</v>
-      </c>
-      <c r="H6" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="M6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="20">
         <v>1</v>
       </c>
     </row>
@@ -1591,43 +1566,65 @@
       <c r="J7" s="15"/>
       <c r="K7" s="16"/>
       <c r="L7" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="28.5" spans="1:14">
+      <c r="A8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="14">
+        <v>500002</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:14">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="16"/>
+      <c r="D8" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
     </row>
-    <row r="9" s="3" customFormat="1" ht="28.5" spans="1:14">
+    <row r="9" ht="28.5" spans="1:14">
       <c r="A9" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="14">
-        <v>500002</v>
+        <v>500003</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>34</v>
@@ -1645,65 +1642,63 @@
         <v>1</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
+        <v>50</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
     </row>
-    <row r="10" ht="28.5" spans="1:14">
-      <c r="A10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="14">
-        <v>500003</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="15">
-        <v>1</v>
-      </c>
-      <c r="H10" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <v>1</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>51</v>
-      </c>
+    <row r="10" spans="1:14">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
+      <c r="A11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="14">
+        <v>510001</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -1713,19 +1708,19 @@
         <v>31</v>
       </c>
       <c r="B12" s="14">
-        <v>510001</v>
+        <v>520001</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G12" s="15">
         <v>1</v>
@@ -1738,7 +1733,7 @@
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
@@ -1749,19 +1744,19 @@
         <v>31</v>
       </c>
       <c r="B13" s="14">
-        <v>520001</v>
+        <v>530001</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="15">
         <v>1</v>
@@ -1774,44 +1769,13 @@
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="14">
-        <v>530001</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="15">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
-        <v>1</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -1821,48 +1785,79 @@
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" ht="28.5" spans="1:14">
+      <c r="A16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540001</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
+        <v>1</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
     </row>
-    <row r="17" ht="28.5" spans="1:14">
-      <c r="A17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="14">
-        <v>540001</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="15">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="15">
-        <v>1</v>
-      </c>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16" t="s">
-        <v>65</v>
-      </c>
+    <row r="17" spans="1:14">
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
     </row>
     <row r="18" spans="1:14">
+      <c r="A18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="14">
+        <v>510002</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>1</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
@@ -1872,19 +1867,19 @@
         <v>31</v>
       </c>
       <c r="B19" s="14">
-        <v>510002</v>
+        <v>520002</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G19" s="15">
         <v>1</v>
@@ -1908,19 +1903,19 @@
         <v>31</v>
       </c>
       <c r="B20" s="14">
-        <v>520002</v>
+        <v>530002</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
@@ -1938,49 +1933,13 @@
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="14">
-        <v>530002</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="15">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="15">
-        <v>1</v>
-      </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L1:N1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E17 E6:E14 E19:E21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16 E5:E13 E18:E20">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
